--- a/data/templates/项目需求清单-模板.xlsx
+++ b/data/templates/项目需求清单-模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="12111" windowHeight="19251" activeTab="1"/>
+    <workbookView windowWidth="18351" windowHeight="8211" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="项目信息概览" sheetId="1" r:id="rId1"/>
@@ -1266,6 +1266,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1290,14 +1293,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="177" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1686,52 +1686,52 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:11">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:11">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="5" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1858,68 +1858,68 @@
     <col min="3" max="3" width="25.8198198198198" customWidth="1"/>
     <col min="4" max="4" width="24.7297297297297" customWidth="1"/>
     <col min="5" max="5" width="25.027027027027" customWidth="1"/>
-    <col min="6" max="6" width="29.5135135135135" customWidth="1"/>
-    <col min="7" max="7" width="20.5495495495495" customWidth="1"/>
+    <col min="6" max="6" width="29.5135135135135" style="2" customWidth="1"/>
+    <col min="7" max="7" width="20.5495495495495" style="2" customWidth="1"/>
     <col min="8" max="8" width="27.9099099099099" customWidth="1"/>
     <col min="9" max="9" width="33.6396396396396" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24.85" spans="1:9">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
     </row>
     <row r="2" s="1" customFormat="1" ht="50" customHeight="1" spans="1:9">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="15" spans="1:9">
-      <c r="A3" s="6">
+      <c r="A3" s="7">
         <v>1</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="10" t="s">
         <v>32</v>
       </c>
       <c r="F3" s="10" t="s">
@@ -1928,38 +1928,38 @@
       <c r="G3" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="10">
         <v>121</v>
       </c>
-      <c r="I3" s="9">
+      <c r="I3" s="10">
         <v>241</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="15" spans="1:9">
-      <c r="A4" s="6">
+      <c r="A4" s="7">
         <v>2</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
       <c r="F4" s="10" t="s">
         <v>34</v>
       </c>
       <c r="G4" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="15" spans="1:9">
-      <c r="A5" s="6">
+      <c r="A5" s="7">
         <v>5</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9" t="s">
+      <c r="B5" s="8"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10" t="s">
         <v>35</v>
       </c>
       <c r="F5" s="10" t="s">
@@ -1968,34 +1968,34 @@
       <c r="G5" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
     </row>
     <row r="6" s="1" customFormat="1" ht="15" spans="1:9">
-      <c r="A6" s="6">
+      <c r="A6" s="7">
         <v>6</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
       <c r="F6" s="10" t="s">
         <v>37</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
     </row>
     <row r="7" s="1" customFormat="1" ht="15" spans="1:9">
-      <c r="A7" s="6">
+      <c r="A7" s="7">
         <v>7</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9" t="s">
+      <c r="B7" s="8"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10" t="s">
         <v>38</v>
       </c>
       <c r="F7" s="10" t="s">
@@ -2004,33 +2004,33 @@
       <c r="G7" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
     </row>
     <row r="8" ht="15" spans="1:9">
-      <c r="A8" s="6">
+      <c r="A8" s="7">
         <v>8</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
       <c r="F8" s="12" t="s">
         <v>40</v>
       </c>
       <c r="G8" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
     </row>
     <row r="9" ht="15" spans="1:9">
-      <c r="A9" s="6">
+      <c r="A9" s="7">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="9"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="10"/>
       <c r="E9" s="13" t="s">
         <v>41</v>
       </c>
@@ -2040,16 +2040,16 @@
       <c r="G9" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
     </row>
     <row r="10" ht="15" spans="1:9">
-      <c r="A10" s="6">
+      <c r="A10" s="7">
         <v>10</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="9"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="10"/>
       <c r="E10" s="13" t="s">
         <v>43</v>
       </c>
@@ -2059,16 +2059,16 @@
       <c r="G10" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
     </row>
     <row r="11" ht="15" spans="1:9">
-      <c r="A11" s="6">
+      <c r="A11" s="7">
         <v>11</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="9"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="10"/>
       <c r="E11" s="13"/>
       <c r="F11" s="12" t="s">
         <v>45</v>
@@ -2076,16 +2076,16 @@
       <c r="G11" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
     </row>
     <row r="12" ht="15" spans="1:9">
-      <c r="A12" s="6">
+      <c r="A12" s="7">
         <v>12</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="9"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="10"/>
       <c r="E12" s="13" t="s">
         <v>46</v>
       </c>
@@ -2095,16 +2095,16 @@
       <c r="G12" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
     </row>
     <row r="13" ht="15" spans="1:9">
-      <c r="A13" s="6">
+      <c r="A13" s="7">
         <v>13</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="9"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="10"/>
       <c r="E13" s="13"/>
       <c r="F13" s="12" t="s">
         <v>48</v>
@@ -2112,13 +2112,13 @@
       <c r="G13" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
     </row>
     <row r="14" ht="15" spans="1:9">
-      <c r="A14" s="6"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="8"/>
+      <c r="A14" s="7"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="9"/>
       <c r="D14" s="14" t="s">
         <v>49</v>
       </c>
@@ -2131,15 +2131,15 @@
       <c r="G14" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
     </row>
     <row r="15" ht="15" spans="1:9">
-      <c r="A15" s="6">
+      <c r="A15" s="7">
         <v>14</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="9"/>
       <c r="D15" s="16"/>
       <c r="E15" s="17"/>
       <c r="F15" s="12" t="s">
@@ -2148,13 +2148,13 @@
       <c r="G15" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
     </row>
     <row r="16" ht="15" spans="1:9">
-      <c r="A16" s="6"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="8"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="9"/>
       <c r="D16" s="16"/>
       <c r="E16" s="17"/>
       <c r="F16" s="12" t="s">
@@ -2163,15 +2163,15 @@
       <c r="G16" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
     </row>
     <row r="17" ht="15" spans="1:9">
-      <c r="A17" s="6">
+      <c r="A17" s="7">
         <v>15</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="9"/>
       <c r="D17" s="16"/>
       <c r="E17" s="17"/>
       <c r="F17" s="12" t="s">
@@ -2180,15 +2180,15 @@
       <c r="G17" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
     </row>
     <row r="18" ht="15" spans="1:9">
-      <c r="A18" s="6">
+      <c r="A18" s="7">
         <v>16</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="9"/>
       <c r="D18" s="16"/>
       <c r="E18" s="17"/>
       <c r="F18" s="12" t="s">
@@ -2197,15 +2197,15 @@
       <c r="G18" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
     </row>
     <row r="19" ht="15" spans="1:9">
-      <c r="A19" s="6">
+      <c r="A19" s="7">
         <v>17</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="9"/>
       <c r="D19" s="16"/>
       <c r="E19" s="17"/>
       <c r="F19" s="12" t="s">
@@ -2214,15 +2214,15 @@
       <c r="G19" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
     </row>
     <row r="20" ht="15" spans="1:9">
-      <c r="A20" s="6">
+      <c r="A20" s="7">
         <v>18</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="9"/>
       <c r="D20" s="18"/>
       <c r="E20" s="19"/>
       <c r="F20" s="12" t="s">
@@ -2231,8 +2231,8 @@
       <c r="G20" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="13">

--- a/data/templates/项目需求清单-模板.xlsx
+++ b/data/templates/项目需求清单-模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18351" windowHeight="8211" activeTab="1"/>
+    <workbookView windowWidth="32065" windowHeight="14725"/>
   </bookViews>
   <sheets>
     <sheet name="项目信息概览" sheetId="1" r:id="rId1"/>
@@ -1259,7 +1259,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1299,9 +1299,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1318,9 +1315,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1672,17 +1666,17 @@
   <dimension ref="A1:K14"/>
   <sheetFormatPr defaultColWidth="8.75675675675676" defaultRowHeight="14.1"/>
   <cols>
-    <col min="1" max="1" width="5.5045045045045" style="20" customWidth="1"/>
-    <col min="2" max="2" width="20.6306306306306" style="20" customWidth="1"/>
-    <col min="3" max="3" width="41.2522522522523" style="20" customWidth="1"/>
-    <col min="4" max="4" width="18.0540540540541" style="20" customWidth="1"/>
-    <col min="5" max="5" width="19.4684684684685" style="20" customWidth="1"/>
-    <col min="6" max="6" width="13.5045045045045" style="20" customWidth="1"/>
-    <col min="7" max="7" width="17.6306306306306" style="20" customWidth="1"/>
-    <col min="8" max="8" width="19.2252252252252" style="20" customWidth="1"/>
-    <col min="9" max="9" width="27.3873873873874" style="20" customWidth="1"/>
-    <col min="10" max="10" width="28.0540540540541" style="20" customWidth="1"/>
-    <col min="11" max="11" width="24.027027027027" style="20" customWidth="1"/>
+    <col min="1" max="1" width="5.5045045045045" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.6306306306306" style="2" customWidth="1"/>
+    <col min="3" max="3" width="41.2522522522523" style="2" customWidth="1"/>
+    <col min="4" max="4" width="18.0540540540541" style="2" customWidth="1"/>
+    <col min="5" max="5" width="19.4684684684685" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.5045045045045" style="2" customWidth="1"/>
+    <col min="7" max="7" width="17.6306306306306" style="2" customWidth="1"/>
+    <col min="8" max="8" width="19.2252252252252" style="2" customWidth="1"/>
+    <col min="9" max="9" width="27.3873873873874" style="2" customWidth="1"/>
+    <col min="10" max="10" width="28.0540540540541" style="2" customWidth="1"/>
+    <col min="11" max="11" width="24.027027027027" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:11">
@@ -1736,91 +1730,91 @@
       </c>
     </row>
     <row r="3" ht="30" spans="1:11">
-      <c r="A3" s="21">
+      <c r="A3" s="19">
         <v>1</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="24" t="s">
+      <c r="D3" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="24" t="s">
+      <c r="F3" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="24" t="s">
+      <c r="G3" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="24" t="s">
+      <c r="H3" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="24">
+      <c r="I3" s="22">
         <v>13950406998</v>
       </c>
-      <c r="J3" s="24">
+      <c r="J3" s="22">
         <v>121</v>
       </c>
-      <c r="K3" s="24">
+      <c r="K3" s="22">
         <v>181.5</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:11">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="24">
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="22">
         <f>SUM(J3:J3)</f>
         <v>121</v>
       </c>
-      <c r="K4" s="24">
+      <c r="K4" s="22">
         <f>SUM(K3:K3)</f>
         <v>181.5</v>
       </c>
     </row>
     <row r="5" ht="15" spans="1:11">
-      <c r="B5" s="27"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="27"/>
-      <c r="K5" s="27"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="25"/>
     </row>
     <row r="7" hidden="1" spans="1:11">
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="8" hidden="1" spans="1:11">
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="9" hidden="1" spans="1:11">
-      <c r="E9" s="20" t="s">
+      <c r="E9" s="2" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2031,7 +2025,7 @@
       <c r="B9" s="8"/>
       <c r="C9" s="9"/>
       <c r="D9" s="10"/>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="12" t="s">
         <v>41</v>
       </c>
       <c r="F9" s="12" t="s">
@@ -2050,7 +2044,7 @@
       <c r="B10" s="8"/>
       <c r="C10" s="9"/>
       <c r="D10" s="10"/>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="12" t="s">
         <v>43</v>
       </c>
       <c r="F10" s="12" t="s">
@@ -2069,7 +2063,7 @@
       <c r="B11" s="8"/>
       <c r="C11" s="9"/>
       <c r="D11" s="10"/>
-      <c r="E11" s="13"/>
+      <c r="E11" s="12"/>
       <c r="F11" s="12" t="s">
         <v>45</v>
       </c>
@@ -2086,7 +2080,7 @@
       <c r="B12" s="8"/>
       <c r="C12" s="9"/>
       <c r="D12" s="10"/>
-      <c r="E12" s="13" t="s">
+      <c r="E12" s="12" t="s">
         <v>46</v>
       </c>
       <c r="F12" s="12" t="s">
@@ -2105,7 +2099,7 @@
       <c r="B13" s="8"/>
       <c r="C13" s="9"/>
       <c r="D13" s="10"/>
-      <c r="E13" s="13"/>
+      <c r="E13" s="12"/>
       <c r="F13" s="12" t="s">
         <v>48</v>
       </c>
@@ -2119,10 +2113,10 @@
       <c r="A14" s="7"/>
       <c r="B14" s="8"/>
       <c r="C14" s="9"/>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E14" s="14" t="s">
         <v>32</v>
       </c>
       <c r="F14" s="12" t="s">
@@ -2140,8 +2134,8 @@
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="9"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="17"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="16"/>
       <c r="F15" s="12" t="s">
         <v>51</v>
       </c>
@@ -2155,8 +2149,8 @@
       <c r="A16" s="7"/>
       <c r="B16" s="8"/>
       <c r="C16" s="9"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="17"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="16"/>
       <c r="F16" s="12" t="s">
         <v>52</v>
       </c>
@@ -2172,8 +2166,8 @@
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="9"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="17"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="16"/>
       <c r="F17" s="12" t="s">
         <v>53</v>
       </c>
@@ -2189,8 +2183,8 @@
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="9"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="17"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="16"/>
       <c r="F18" s="12" t="s">
         <v>54</v>
       </c>
@@ -2206,8 +2200,8 @@
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="9"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="17"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="16"/>
       <c r="F19" s="12" t="s">
         <v>55</v>
       </c>
@@ -2223,8 +2217,8 @@
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="9"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="19"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="18"/>
       <c r="F20" s="12" t="s">
         <v>56</v>
       </c>

--- a/data/templates/项目需求清单-模板.xlsx
+++ b/data/templates/项目需求清单-模板.xlsx
@@ -1948,7 +1948,7 @@
     </row>
     <row r="5" s="1" customFormat="1" ht="15" spans="1:9">
       <c r="A5" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="9"/>
@@ -1967,7 +1967,7 @@
     </row>
     <row r="6" s="1" customFormat="1" ht="15" spans="1:9">
       <c r="A6" s="7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="9"/>
@@ -1984,7 +1984,7 @@
     </row>
     <row r="7" s="1" customFormat="1" ht="15" spans="1:9">
       <c r="A7" s="7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="9"/>
@@ -2003,7 +2003,7 @@
     </row>
     <row r="8" ht="15" spans="1:9">
       <c r="A8" s="7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="9"/>
@@ -2020,7 +2020,7 @@
     </row>
     <row r="9" ht="15" spans="1:9">
       <c r="A9" s="7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="9"/>
@@ -2039,7 +2039,7 @@
     </row>
     <row r="10" ht="15" spans="1:9">
       <c r="A10" s="7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="9"/>
@@ -2058,7 +2058,7 @@
     </row>
     <row r="11" ht="15" spans="1:9">
       <c r="A11" s="7">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="9"/>
@@ -2075,7 +2075,7 @@
     </row>
     <row r="12" ht="15" spans="1:9">
       <c r="A12" s="7">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="9"/>
@@ -2094,7 +2094,7 @@
     </row>
     <row r="13" ht="15" spans="1:9">
       <c r="A13" s="7">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="9"/>
@@ -2110,7 +2110,9 @@
       <c r="I13" s="10"/>
     </row>
     <row r="14" ht="15" spans="1:9">
-      <c r="A14" s="7"/>
+      <c r="A14" s="7">
+        <v>12</v>
+      </c>
       <c r="B14" s="8"/>
       <c r="C14" s="9"/>
       <c r="D14" s="13" t="s">
@@ -2130,7 +2132,7 @@
     </row>
     <row r="15" ht="15" spans="1:9">
       <c r="A15" s="7">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="9"/>
@@ -2146,7 +2148,9 @@
       <c r="I15" s="10"/>
     </row>
     <row r="16" ht="15" spans="1:9">
-      <c r="A16" s="7"/>
+      <c r="A16" s="7">
+        <v>14</v>
+      </c>
       <c r="B16" s="8"/>
       <c r="C16" s="9"/>
       <c r="D16" s="15"/>
